--- a/data_raw/fortalecimiento_municipal/kobo_mensual_raw.xlsx
+++ b/data_raw/fortalecimiento_municipal/kobo_mensual_raw.xlsx
@@ -7,7 +7,12 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Fortalecimiento municipal - ..." sheetId="1" r:id="rId1"/>
+    <sheet name="rep_capacitacion" sheetId="2" r:id="rId2"/>
+    <sheet name="rep_asistencia" sheetId="3" r:id="rId3"/>
+    <sheet name="rep_estudio" sheetId="4" r:id="rId4"/>
+    <sheet name="rep_pirds" sheetId="5" r:id="rId5"/>
+    <sheet name="rep_reunion" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,6 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -44,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -340,9 +349,3406 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:BD5"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>deviceid</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>programa_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>programa_nombre</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>intro</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>anio_reportado</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>nota_anio</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mes_reportado</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>mes_num</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>estado_reporte</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>periodo_clave</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>observaciones_generales</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>modulos_activos</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>modulos_activos/capacitaciones</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>modulos_activos/asistencias</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>modulos_activos/estudios</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>modulos_activos/pirds</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>modulos_activos/reuniones</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>nota_modulos</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>nota_capacitaciones</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>capacitaciones_mes</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>personas_capacitadas_mes</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>resumen_capacitaciones</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>nota_asistencias</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>asistencias_tecnicas_mes</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>resumen_asistencias</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>nota_estudios</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>estudios_caracterizacion_mes</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>resumen_estudios</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>nota_pirds</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>pirds_implementados_mes</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>resumen_pirds</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>nota_reuniones</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>reuniones_mes</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>resumen_reuniones</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>meta_anual_municipios_capacitados</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>meta_anual_personas_capacitadas</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>meta_anual_asistencias_tecnicas</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>meta_anual_estudios_caracterizacion</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>meta_anual_pirds_implementados</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>nota_revision_1</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>nota_revision_2</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>comentarios_revision</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>_id</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>_uuid</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>_submission_time</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>_validation_status</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>_notes</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>_status</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>_submitted_by</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>__version__</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>_tags</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>meta/rootUuid</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46094.04396738426</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46094.04546366898</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46093</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ee.kobotoolbox.org:U6VBRZrqozC5JwCT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>fortalecimiento_municipal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>borrador</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-mar</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>capacitaciones asistencias estudios pirds reuniones</t>
+        </is>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT2">
+        <v>695513400</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+      <c r="AV2" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>uuid:d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+      <c r="BD2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>46094.04546415509</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46094.04715630787</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46093</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ee.kobotoolbox.org:U6VBRZrqozC5JwCT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>fortalecimiento_municipal</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>jul</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>final_validado</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-jul</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>capacitaciones asistencias estudios pirds reuniones</t>
+        </is>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT3">
+        <v>695513408</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+      <c r="AV3" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>uuid:1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+      <c r="BD3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>46094.04715679398</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46094.04776277778</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46093</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ee.kobotoolbox.org:U6VBRZrqozC5JwCT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>fortalecimiento_municipal</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>jun</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>final_validado</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-jun</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>asistencias</t>
+        </is>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT4">
+        <v>695513414</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>9acf8206-b8c8-4880-9762-1b319dd38f7d</t>
+        </is>
+      </c>
+      <c r="AV4" s="1">
+        <v>46094.29804398148</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>uuid:9acf8206-b8c8-4880-9762-1b319dd38f7d</t>
+        </is>
+      </c>
+      <c r="BD4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>46094.0480744676</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46094.04949530093</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46093</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ee.kobotoolbox.org:U6VBRZrqozC5JwCT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>fortalecimiento_municipal</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>feb</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>final_validado</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-feb</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>capacitaciones asistencias estudios pirds reuniones</t>
+        </is>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT5">
+        <v>695515808</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+      <c r="AV5" s="1">
+        <v>46094.29949074074</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>uuid:b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+      <c r="BD5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AZ4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_capacitacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/concepcion</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/nahuala</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/panajachel</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/san_andres_semetabaj</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/san_antonio_palopo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/san_jose_chacaya</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/santa_catarina_ixtahuacan</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/santa_catarina_palopo</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/santa_clara_la_laguna</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/santa_cruz_la_laguna</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/santa_lucia_utatlan</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/santa_maria_visitacion</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/santiago_atitlan</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/san_juan_la_laguna</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/san_lucas_toliman</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/san_marcos_la_laguna</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/san_pablo_la_laguna</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/san_pedro_la_laguna</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>municipios_capacitacion/solola</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>modalidad_capacitacion</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>tipo_capacitacion</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>temas_capacitacion</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>temas_capacitacion/snip</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>temas_capacitacion/sig</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temas_capacitacion/recoleccion_digital</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>temas_capacitacion/cumplimiento_legal</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>temas_capacitacion/saneamiento_agua</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>temas_capacitacion/otro</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>participantes_total</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>participantes_tecnicos</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>participantes_operarios</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>participantes_otro</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>instituciones_participantes</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>evidencia_capacitacion</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>observaciones_capacitacion</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>participantes_subtotal</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>nota_subtotal_capacitacion</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>_parent_table_name</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>_parent_index</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>_submission__id</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>_submission__uuid</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>_submission__submission_time</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>_submission__validation_status</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>_submission__notes</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>_submission__status</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>_submission__submitted_by</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>_submission___version__</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>_submission__tags</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>_submission_meta/rootUuid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>panajachel</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>virtual</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>capacitacion</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>recoleccion_digital</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>34</v>
+      </c>
+      <c r="AF2">
+        <v>21</v>
+      </c>
+      <c r="AG2">
+        <v>34</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>695513400</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+      <c r="AS2" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>uuid:d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>san_antonio_palopo</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>virtual</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>socializacion</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>recoleccion_digital</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>32</v>
+      </c>
+      <c r="AF3">
+        <v>21</v>
+      </c>
+      <c r="AG3">
+        <v>23</v>
+      </c>
+      <c r="AH3">
+        <v>56</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AN3">
+        <v>2</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="AP3">
+        <v>2</v>
+      </c>
+      <c r="AQ3">
+        <v>695513408</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+      <c r="AS3" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>uuid:1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>panajachel</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>asesoria_grupal</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>cumplimiento_legal</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>12</v>
+      </c>
+      <c r="AF4">
+        <v>23</v>
+      </c>
+      <c r="AG4">
+        <v>32</v>
+      </c>
+      <c r="AH4">
+        <v>23</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AN4">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="AP4">
+        <v>4</v>
+      </c>
+      <c r="AQ4">
+        <v>695515808</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+      <c r="AS4" s="1">
+        <v>46094.29949074074</v>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>uuid:b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AD5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_asistencia</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>municipio_asistencia</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>proyecto_codigo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>nombre_corto_proyecto</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sector_asistencia</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sector_asistencia/alcantarillado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sector_asistencia/aguas_residuales</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sector_asistencia/desechos_solidos</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sector_asistencia/agua_potable</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sector_asistencia/otro</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>movimiento_asistencia</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>etapa_proyecto</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>cuenta_nueva_asistencia</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>resultado_asistencia</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>evidencia_asistencia</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>observaciones_asistencia</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>nueva_asistencia_flag</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>_parent_table_name</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>_parent_index</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>_submission__id</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>_submission__uuid</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>_submission__submission_time</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>_submission__validation_status</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>_submission__notes</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>_submission__status</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>_submission__submitted_by</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>_submission___version__</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>_submission__tags</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>_submission_meta/rootUuid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>san_jose_chacaya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>aguas_residuales</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>seguimiento</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>formulacion</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>695513400</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+      <c r="W2" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>uuid:d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>san_antonio_palopo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>alcantarillado</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nueva</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>diagnostico</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="T3">
+        <v>2</v>
+      </c>
+      <c r="U3">
+        <v>695513408</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+      <c r="W3" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>uuid:1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>san_antonio_palopo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>alcantarillado</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nueva</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>diagnostico</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4">
+        <v>3</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>695513414</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>9acf8206-b8c8-4880-9762-1b319dd38f7d</t>
+        </is>
+      </c>
+      <c r="W4" s="1">
+        <v>46094.29804398148</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>uuid:9acf8206-b8c8-4880-9762-1b319dd38f7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>panajachel</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>alcantarillado</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>nueva</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>diagnostico</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5">
+        <v>4</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="T5">
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <v>695515808</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+      <c r="W5" s="1">
+        <v>46094.29949074074</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>uuid:b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AA4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_estudio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>municipio_estudio</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector_estudio</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sector_estudio/comercial</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sector_estudio/mercados</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sector_estudio/domiciliar</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sector_estudio/mixto</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sector_estudio/otro</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>estado_estudio</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>estudio_finalizado_mes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>instituciones_apoyo_estudio</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>evidencia_estudio</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>observaciones_estudio</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>estudio_finalizado_flag</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>_parent_table_name</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>_parent_index</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>_submission__id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>_submission__uuid</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>_submission__submission_time</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>_submission__validation_status</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>_submission__notes</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>_submission__status</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>_submission__submitted_by</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>_submission___version__</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>_submission__tags</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>_submission_meta/rootUuid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>san_juan_la_laguna</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>mercados</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>planificacion</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>695513400</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+      <c r="T2" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>uuid:d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>san_juan_la_laguna</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>comercial</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>levantamiento</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3">
+        <v>2</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3">
+        <v>695513408</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+      <c r="T3" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>uuid:1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>san_andres_semetabaj</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>comercial mercados</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>planificacion</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="Q4">
+        <v>4</v>
+      </c>
+      <c r="R4">
+        <v>695515808</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+      <c r="T4" s="1">
+        <v>46094.29949074074</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>uuid:b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:U4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_pirds</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>municipio_pirds</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>estado_pirds</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pirds_implementado_mes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>requiere_seguimiento_pirds</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>evidencia_pirds</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>observaciones_pirds</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pirds_implementado_flag</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>_parent_table_name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>_parent_index</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>_submission__id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>_submission__uuid</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>_submission__submission_time</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>_submission__validation_status</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>_submission__notes</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>_submission__status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>_submission__submitted_by</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>_submission___version__</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>_submission__tags</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>_submission_meta/rootUuid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>san_jose_chacaya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>diagnostico</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>695513400</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+      <c r="N2" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>uuid:d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>san_antonio_palopo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>acercamiento</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>695513408</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+      <c r="N3" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>uuid:1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>san_antonio_palopo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>actualizacion</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>695515808</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+      <c r="N4" s="1">
+        <v>46094.29949074074</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>uuid:b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AM4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_reunion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tipo_reunion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>municipios_reunion</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/concepcion</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/nahuala</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/panajachel</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/san_andres_semetabaj</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/san_antonio_palopo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/san_jose_chacaya</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/santa_catarina_ixtahuacan</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/santa_catarina_palopo</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/santa_clara_la_laguna</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/santa_cruz_la_laguna</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/santa_lucia_utatlan</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/santa_maria_visitacion</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/santiago_atitlan</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/san_juan_la_laguna</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/san_lucas_toliman</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/san_marcos_la_laguna</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/san_pablo_la_laguna</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/san_pedro_la_laguna</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>municipios_reunion/solola</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>tema_reunion</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>instituciones_presentes</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>acuerdos_reunion</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>evidencia_reunion</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>_parent_table_name</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>_parent_index</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>_submission__id</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>_submission__uuid</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>_submission__submission_time</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>_submission__validation_status</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>_submission__notes</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>_submission__status</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>_submission__submitted_by</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>_submission___version__</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>_submission__tags</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>_submission_meta/rootUuid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>reunion_incidencia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>santa_catarina_palopo santa_clara_la_laguna santa_cruz_la_laguna</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>695513400</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+      <c r="AF2" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>uuid:d0d298a6-61f7-47aa-85b1-552cf5a59907</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>eje_agua_saneamiento_codema</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>concepcion panajachel san_antonio_palopo santa_catarina_ixtahuacan</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="AC3">
+        <v>2</v>
+      </c>
+      <c r="AD3">
+        <v>695513408</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+      <c r="AF3" s="1">
+        <v>46094.29803240741</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>uuid:1d56c094-d756-4661-8772-83ab95ea1cb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mesa_tecnica_departamental</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>santa_catarina_ixtahuacan</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Fortalecimiento municipal - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="AC4">
+        <v>4</v>
+      </c>
+      <c r="AD4">
+        <v>695515808</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+      <c r="AF4" s="1">
+        <v>46094.29949074074</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>vP2WbyB5WN2CWVEvkupKZP</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>uuid:b8ec1965-7cd6-443b-b4c4-8e9ad693bc18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>